--- a/tabular/core/flavi-ncbi-refseqs-side-data.xlsx
+++ b/tabular/core/flavi-ncbi-refseqs-side-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Flavivirus-GLUE/tabular/core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939360CA-5325-3B43-9D18-58BE6B3CA950}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE64AD68-D61A-7048-89F1-CBD6D53747C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4470,31 +4470,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4744,6 +4719,31 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -4780,29 +4780,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BA8C5DC3-A657-504B-8CEA-EF989E4182D4}" name="Table1" displayName="Table1" ref="A1:T249" totalsRowShown="0" headerRowDxfId="21" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BA8C5DC3-A657-504B-8CEA-EF989E4182D4}" name="Table1" displayName="Table1" ref="A1:T249" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:T249" xr:uid="{99F1C8DD-5402-7447-BEC2-7788F394BEB4}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{F5C9B291-0361-824A-9D39-03112C754322}" name="sequenceID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{1CCE920A-ADAE-A54B-AC30-C0D2EB4F41EA}" name="name" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{8512F77A-F993-F945-9BEC-FDCAB18C830D}" name="full_name" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{CFB1A2F2-0463-E848-9E45-405450252B9D}" name="subfamily" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{73B68BDD-7AB5-DE45-92CD-D6735C99E72F}" name="supergenus" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{917C0BFE-8641-E948-9A61-0FCDDE7D1C90}" name="genus" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{82BB9ADB-470B-A24A-8B0C-8310364E995E}" name="subgenus" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{231B0150-4A5F-474A-97AE-555679959219}" name="clade" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{A9F7333B-C0E1-1D45-99AB-A67739EA4D3C}" name="host_major_group" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{CDF07F39-492F-1D46-B764-FD91491A5393}" name="host_minor_group" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{52367994-2768-3D44-986A-17583FA2B11D}" name="isolation_host" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{A0E64D07-4150-B44F-B1B3-CC631180C6B0}" name="vector_group" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{F7FB6D4A-E7B0-064E-9823-A4B07F7970D9}" name="reservoir_group" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{CED0AD26-ED2A-9B48-A13E-96CD4A9F5F23}" name="isolate" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{BC1EDEDB-A6E7-CC4A-B20F-C8F501C96C23}" name="country" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{1277AB03-A8F9-6B4D-B65A-4F822C69F08C}" name="place_sampled" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{9108682E-3FDC-8A42-BFAC-D776DBD2899A}" name="collection_year" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{5EF0188C-941C-AE49-9CD7-AD8C98FA12CD}" name="collection_month" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{DE40A557-7817-2E46-A282-198A69EC74A0}" name="collection_month_day" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{D6D156F2-DFA2-534E-BBB1-DA1B12CE2C09}" name="sampled_host_common_name" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F5C9B291-0361-824A-9D39-03112C754322}" name="sequenceID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{1CCE920A-ADAE-A54B-AC30-C0D2EB4F41EA}" name="name" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{8512F77A-F993-F945-9BEC-FDCAB18C830D}" name="full_name" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{CFB1A2F2-0463-E848-9E45-405450252B9D}" name="subfamily" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{73B68BDD-7AB5-DE45-92CD-D6735C99E72F}" name="supergenus" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{917C0BFE-8641-E948-9A61-0FCDDE7D1C90}" name="genus" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{82BB9ADB-470B-A24A-8B0C-8310364E995E}" name="subgenus" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{231B0150-4A5F-474A-97AE-555679959219}" name="clade" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{A9F7333B-C0E1-1D45-99AB-A67739EA4D3C}" name="host_major_group" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{CDF07F39-492F-1D46-B764-FD91491A5393}" name="host_minor_group" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{52367994-2768-3D44-986A-17583FA2B11D}" name="isolation_host" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{A0E64D07-4150-B44F-B1B3-CC631180C6B0}" name="vector_group" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FB6D4A-E7B0-064E-9823-A4B07F7970D9}" name="reservoir_group" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{CED0AD26-ED2A-9B48-A13E-96CD4A9F5F23}" name="isolate" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{BC1EDEDB-A6E7-CC4A-B20F-C8F501C96C23}" name="country" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{1277AB03-A8F9-6B4D-B65A-4F822C69F08C}" name="place_sampled" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{9108682E-3FDC-8A42-BFAC-D776DBD2899A}" name="collection_year" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{5EF0188C-941C-AE49-9CD7-AD8C98FA12CD}" name="collection_month" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{DE40A557-7817-2E46-A282-198A69EC74A0}" name="collection_month_day" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{D6D156F2-DFA2-534E-BBB1-DA1B12CE2C09}" name="sampled_host_common_name" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
